--- a/estadisticas/arch/dtrp2.xlsx
+++ b/estadisticas/arch/dtrp2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEIMONT\Documents\2021\super\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATOS-EXT/proyectos/Gestor documental Universidad Militar/ArgoUMNG/src/2/estadisticas/arch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2D0510-10A7-421B-9AE6-2AF920099D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31340709-A386-0B4A-8BE3-8B9613C30564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15990" xr2:uid="{DCCD86FB-7485-4760-AE19-9F57E802B0C3}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="16000" xr2:uid="{DCCD86FB-7485-4760-AE19-9F57E802B0C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <t>[a.RFECH]</t>
   </si>
   <si>
-    <t>Medio de Recepción</t>
+    <t>/Volumes/DATOS-EXT/proyectos/Gestor documental Universidad Militar/ArgoUMNG/src/2/estadisticas/arch/rp9.xlsx</t>
   </si>
 </sst>
 </file>
@@ -737,11 +737,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -842,61 +840,44 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>2276475</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>93378</xdr:rowOff>
+      <xdr:colOff>984315</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1" descr="Logo SuperArgo">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AADA4356-D5E4-4FAC-B340-E7DB731E0379}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC21AD5-BABD-A5DA-D722-019022D98980}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="0"/>
-          <a:ext cx="3152775" cy="817278"/>
+          <a:off x="1778000" y="0"/>
+          <a:ext cx="946215" cy="927100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -905,9 +886,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -945,7 +926,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1051,7 +1032,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1193,7 +1174,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1201,90 +1182,90 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B63DF49-11A9-4999-8E10-DB6A1A62160F}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:H6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="21.5" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="17" t="s">
+    <row r="1" spans="2:8" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
-    <row r="2" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="5" t="s">
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="6" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="8" t="s">
+    <row r="3" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="9" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
+    <row r="4" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1304,104 +1285,6 @@
         <v>16</v>
       </c>
       <c r="H6" s="1"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
